--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2816385-92B4-4BAE-8B2F-74C2B0055A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDEA5D2-D68B-47A7-A208-64615770C82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Vendor Data" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3420" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3458" uniqueCount="699">
   <si>
     <t>Unique Vendor ID</t>
   </si>
@@ -2155,6 +2155,12 @@
   </si>
   <si>
     <t>Siemens Tech Pune</t>
+  </si>
+  <si>
+    <t>Mansukh</t>
+  </si>
+  <si>
+    <t>Firewood Biryani</t>
   </si>
 </sst>
 </file>
@@ -2162,8 +2168,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -2310,7 +2316,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2416,11 +2422,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2500,7 +2519,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2512,7 +2531,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2533,7 +2552,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2551,7 +2570,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2563,16 +2582,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2619,6 +2638,12 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -25134,7 +25159,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32C6D7F0-2556-47D2-8A56-3AC387C2EE46}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -25563,67 +25588,319 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="58">
+      <c r="A14" s="70">
         <v>108</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="70" t="s">
         <v>547</v>
       </c>
-      <c r="D14" s="58">
-        <v>0</v>
-      </c>
-      <c r="E14" s="58" t="s">
+      <c r="D14" s="70">
+        <v>0</v>
+      </c>
+      <c r="E14" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="58">
+      <c r="F14" s="70">
         <v>5</v>
       </c>
-      <c r="G14" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="58">
+      <c r="G14" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="70">
         <v>5</v>
       </c>
-      <c r="I14" s="59">
+      <c r="I14" s="71">
         <v>46118</v>
       </c>
-      <c r="J14" s="58">
+      <c r="J14" s="70">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="58">
+      <c r="A15" s="72">
         <v>53</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="58" t="s">
+      <c r="D15" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="E15" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="58">
+      <c r="E15" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="72">
         <v>16</v>
       </c>
-      <c r="G15" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="58">
-        <v>15</v>
-      </c>
-      <c r="I15" s="59">
+      <c r="G15" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="72">
+        <v>15</v>
+      </c>
+      <c r="I15" s="73">
         <v>46118</v>
       </c>
-      <c r="J15" s="58">
-        <v>15</v>
+      <c r="J15" s="72">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="74">
+        <v>4</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="74">
+        <v>0</v>
+      </c>
+      <c r="G16" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="74">
+        <v>15</v>
+      </c>
+      <c r="I16" s="75">
+        <v>46118</v>
+      </c>
+      <c r="J16" s="74">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="74">
+        <v>18</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="74">
+        <v>0</v>
+      </c>
+      <c r="G17" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="74">
+        <v>15</v>
+      </c>
+      <c r="I17" s="75">
+        <v>46118</v>
+      </c>
+      <c r="J17" s="74">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="74">
+        <v>5</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="74">
+        <v>9</v>
+      </c>
+      <c r="G18" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="74">
+        <v>15</v>
+      </c>
+      <c r="I18" s="75">
+        <v>46118</v>
+      </c>
+      <c r="J18" s="74">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="74">
+        <v>10</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="74">
+        <v>18</v>
+      </c>
+      <c r="G19" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="74">
+        <v>3</v>
+      </c>
+      <c r="I19" s="75">
+        <v>46118</v>
+      </c>
+      <c r="J19" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="74">
+        <v>55</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="74" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="74">
+        <v>2</v>
+      </c>
+      <c r="G20" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="74">
+        <v>5</v>
+      </c>
+      <c r="I20" s="75">
+        <v>46118</v>
+      </c>
+      <c r="J20" s="74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="74">
+        <v>300</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="74" t="s">
+        <v>697</v>
+      </c>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="74">
+        <v>5</v>
+      </c>
+      <c r="G21" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="74">
+        <v>2</v>
+      </c>
+      <c r="I21" s="75">
+        <v>46118</v>
+      </c>
+      <c r="J21" s="74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="74">
+        <v>301</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="74" t="s">
+        <v>698</v>
+      </c>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="74">
+        <v>5</v>
+      </c>
+      <c r="G22" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="74">
+        <v>2</v>
+      </c>
+      <c r="I22" s="75">
+        <v>46118</v>
+      </c>
+      <c r="J22" s="74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="74">
+        <v>51</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="74" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="74">
+        <v>1</v>
+      </c>
+      <c r="G23" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="74">
+        <v>2</v>
+      </c>
+      <c r="I23" s="75">
+        <v>46118</v>
+      </c>
+      <c r="J23" s="74">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B6273C-68E3-4CFE-A06F-1ACB28589914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8307A84B-7003-4622-94E6-9D847F8EB6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
@@ -25167,7 +25167,7 @@
     <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25226,13 +25226,13 @@
         <v>18</v>
       </c>
       <c r="H2" s="58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J2" s="58">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -25261,7 +25261,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J3" s="58">
         <v>21</v>
@@ -25293,7 +25293,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J4" s="58">
         <v>21</v>
@@ -25325,7 +25325,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J5" s="58">
         <v>21</v>
@@ -25354,13 +25354,13 @@
         <v>18</v>
       </c>
       <c r="H6" s="58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J6" s="58">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -25386,13 +25386,13 @@
         <v>18</v>
       </c>
       <c r="H7" s="58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J7" s="58">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -25418,13 +25418,13 @@
         <v>18</v>
       </c>
       <c r="H8" s="58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J8" s="58">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -25453,7 +25453,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J9" s="58">
         <v>15</v>
@@ -25482,13 +25482,13 @@
         <v>18</v>
       </c>
       <c r="H10" s="58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J10" s="58">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -25517,7 +25517,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J11" s="58">
         <v>21</v>
@@ -25546,13 +25546,13 @@
         <v>18</v>
       </c>
       <c r="H12" s="58">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I12" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J12" s="58">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -25581,7 +25581,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="59">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J13" s="58">
         <v>21</v>
@@ -25613,7 +25613,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="71">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J14" s="70">
         <v>21</v>
@@ -25645,7 +25645,7 @@
         <v>2</v>
       </c>
       <c r="I15" s="73">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J15" s="72">
         <v>4</v>
@@ -25677,7 +25677,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="75">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J16" s="74">
         <v>21</v>
@@ -25709,7 +25709,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="75">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J17" s="74">
         <v>21</v>
@@ -25741,7 +25741,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="75">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J18" s="74">
         <v>21</v>
@@ -25773,7 +25773,7 @@
         <v>3</v>
       </c>
       <c r="I19" s="75">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J19" s="74">
         <v>5</v>
@@ -25802,13 +25802,13 @@
         <v>18</v>
       </c>
       <c r="H20" s="74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="75">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J20" s="74">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -25835,7 +25835,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="75">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J21" s="74">
         <v>4</v>
@@ -25865,7 +25865,7 @@
         <v>2</v>
       </c>
       <c r="I22" s="75">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J22" s="74">
         <v>5</v>
@@ -25894,13 +25894,13 @@
         <v>18</v>
       </c>
       <c r="H23" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="75">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="J23" s="74">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8307A84B-7003-4622-94E6-9D847F8EB6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6FCAB8-A919-42D7-83CB-A660CEA14314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Vendor Data" sheetId="1" r:id="rId1"/>
@@ -25220,7 +25220,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G2" s="58" t="s">
         <v>18</v>
@@ -25229,7 +25229,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J2" s="58">
         <v>8</v>
@@ -25261,7 +25261,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J3" s="58">
         <v>21</v>
@@ -25293,7 +25293,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J4" s="58">
         <v>21</v>
@@ -25325,7 +25325,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J5" s="58">
         <v>21</v>
@@ -25348,7 +25348,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="58">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>18</v>
@@ -25357,7 +25357,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J6" s="58">
         <v>7</v>
@@ -25380,19 +25380,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="58">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I7" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J7" s="58">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -25412,19 +25412,19 @@
         <v>18</v>
       </c>
       <c r="F8" s="58">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J8" s="58">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -25450,13 +25450,13 @@
         <v>18</v>
       </c>
       <c r="H9" s="58">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I9" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J9" s="58">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -25485,7 +25485,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J10" s="58">
         <v>4</v>
@@ -25508,16 +25508,16 @@
         <v>23</v>
       </c>
       <c r="F11" s="58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I11" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J11" s="58">
         <v>21</v>
@@ -25546,13 +25546,13 @@
         <v>18</v>
       </c>
       <c r="H12" s="58">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I12" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J12" s="58">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -25581,7 +25581,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="59">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J13" s="58">
         <v>21</v>
@@ -25613,7 +25613,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="71">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J14" s="70">
         <v>21</v>
@@ -25642,13 +25642,13 @@
         <v>18</v>
       </c>
       <c r="H15" s="72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="73">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J15" s="72">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -25677,7 +25677,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="75">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J16" s="74">
         <v>21</v>
@@ -25741,7 +25741,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="75">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J18" s="74">
         <v>21</v>
@@ -25770,13 +25770,13 @@
         <v>18</v>
       </c>
       <c r="H19" s="74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I19" s="75">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J19" s="74">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -25802,13 +25802,13 @@
         <v>18</v>
       </c>
       <c r="H20" s="74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20" s="75">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J20" s="74">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -25897,7 +25897,7 @@
         <v>3</v>
       </c>
       <c r="I23" s="75">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="J23" s="74">
         <v>5</v>
@@ -26284,10 +26284,10 @@
         <v>112</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I13" s="58" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">

--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50DD293-92AB-40D9-85B8-62250D6B2390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145163A9-4551-4EF5-AA5E-7E7B0009CD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Vendor Data" sheetId="1" r:id="rId1"/>
@@ -25227,7 +25227,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J2" s="58">
         <v>8</v>
@@ -25259,7 +25259,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J3" s="58">
         <v>21</v>
@@ -25291,7 +25291,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J4" s="58">
         <v>21</v>
@@ -25323,7 +25323,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J5" s="58">
         <v>21</v>
@@ -25355,7 +25355,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J6" s="58">
         <v>5</v>
@@ -25387,7 +25387,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J7" s="58">
         <v>5</v>
@@ -25419,7 +25419,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J8" s="58">
         <v>5</v>
@@ -25451,7 +25451,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J9" s="58">
         <v>5</v>
@@ -25483,7 +25483,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J10" s="58">
         <v>5</v>
@@ -25515,7 +25515,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J11" s="58">
         <v>21</v>
@@ -25547,7 +25547,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J12" s="58">
         <v>5</v>
@@ -25579,7 +25579,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J13" s="58">
         <v>21</v>
@@ -25611,7 +25611,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J14" s="70">
         <v>21</v>
@@ -25643,7 +25643,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J15" s="71">
         <v>4</v>
@@ -25675,7 +25675,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J16" s="72">
         <v>21</v>
@@ -25707,7 +25707,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J17" s="72">
         <v>21</v>
@@ -25739,7 +25739,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J18" s="72">
         <v>21</v>
@@ -25771,7 +25771,7 @@
         <v>2.5</v>
       </c>
       <c r="I19" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J19" s="72">
         <v>4.5</v>
@@ -25803,7 +25803,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J20" s="72">
         <v>8</v>
@@ -25833,7 +25833,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J21" s="72">
         <v>4</v>
@@ -25863,7 +25863,7 @@
         <v>2</v>
       </c>
       <c r="I22" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J22" s="72">
         <v>5</v>
@@ -25895,7 +25895,7 @@
         <v>2</v>
       </c>
       <c r="I23" s="59">
-        <v>46136</v>
+        <v>46155</v>
       </c>
       <c r="J23" s="72">
         <v>4</v>

--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145163A9-4551-4EF5-AA5E-7E7B0009CD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD3E43F-5BCD-4D97-9252-EAF6B92094E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
@@ -25227,7 +25227,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J2" s="58">
         <v>8</v>
@@ -25259,7 +25259,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J3" s="58">
         <v>21</v>
@@ -25291,7 +25291,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J4" s="58">
         <v>21</v>
@@ -25323,7 +25323,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J5" s="58">
         <v>21</v>
@@ -25355,7 +25355,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J6" s="58">
         <v>5</v>
@@ -25387,7 +25387,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J7" s="58">
         <v>5</v>
@@ -25419,7 +25419,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J8" s="58">
         <v>5</v>
@@ -25451,7 +25451,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J9" s="58">
         <v>5</v>
@@ -25483,7 +25483,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J10" s="58">
         <v>5</v>
@@ -25515,7 +25515,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J11" s="58">
         <v>21</v>
@@ -25547,7 +25547,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J12" s="58">
         <v>5</v>
@@ -25579,7 +25579,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J13" s="58">
         <v>21</v>
@@ -25611,7 +25611,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J14" s="70">
         <v>21</v>
@@ -25643,7 +25643,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J15" s="71">
         <v>4</v>
@@ -25675,7 +25675,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J16" s="72">
         <v>21</v>
@@ -25707,7 +25707,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J17" s="72">
         <v>21</v>
@@ -25739,7 +25739,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J18" s="72">
         <v>21</v>
@@ -25771,7 +25771,7 @@
         <v>2.5</v>
       </c>
       <c r="I19" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J19" s="72">
         <v>4.5</v>
@@ -25803,7 +25803,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J20" s="72">
         <v>8</v>
@@ -25833,7 +25833,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J21" s="72">
         <v>4</v>
@@ -25863,7 +25863,7 @@
         <v>2</v>
       </c>
       <c r="I22" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J22" s="72">
         <v>5</v>
@@ -25895,7 +25895,7 @@
         <v>2</v>
       </c>
       <c r="I23" s="59">
-        <v>46155</v>
+        <v>46136</v>
       </c>
       <c r="J23" s="72">
         <v>4</v>
